--- a/data/trans_orig/IP13_R1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121793</t>
+          <t>122665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117283</t>
+          <t>115731</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>125582</t>
+          <t>125644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>242478</t>
+          <t>242895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252068</t>
+          <t>252227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53553</t>
+          <t>53704</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63767</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119645</t>
+          <t>119502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124877</t>
+          <t>124777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65503</t>
+          <t>65510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72605</t>
+          <t>72905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141875</t>
+          <t>142163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37494</t>
+          <t>36679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71939</t>
+          <t>71497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>538</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45628</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54154</t>
+          <t>54376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96945</t>
+          <t>96763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101815</t>
+          <t>101718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>796</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114841</t>
+          <t>114340</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122293</t>
+          <t>122305</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148377</t>
+          <t>147898</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154514</t>
+          <t>154492</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>265803</t>
+          <t>266275</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>275775</t>
+          <t>275894</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129029</t>
+          <t>129381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>152468</t>
+          <t>151480</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>283711</t>
+          <t>283567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,47 +3489,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>6812</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>19822</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>11864</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>6848</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>19006</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31003</t>
+          <t>31705</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>648500</t>
+          <t>648397</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>659426</t>
+          <t>659367</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,49 +3602,49 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>749384</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>741426</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>754436</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>749384</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>742242</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>754400</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>1886</t>
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1395585</t>
+          <t>1394883</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1411857</t>
+          <t>1411108</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_R1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R1_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>56481</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>79366</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>198</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4568</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10173</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4174</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4952</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11865</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11533</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111267</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105662</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>114329</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,06%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>126024</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>122665</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>99860</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>97190</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100550</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>122644</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>115731</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>125644</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>290</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>248668</t>
+          <t>211128</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>242895</t>
+          <t>204852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252227</t>
+          <t>214175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>910</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58467</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56284</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>56894</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53704</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>55220</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>51792</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>91,57%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>66065</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>63398</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>67163</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,39%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>194</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>122958</t>
+          <t>113687</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119502</t>
+          <t>110278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124777</t>
+          <t>115301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>987</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1862,74 +1862,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71183</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66416</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>69195</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>65510</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>69857</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>65790</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>70844</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>77166</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>72905</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>78134</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,31%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>160</t>
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>146362</t>
+          <t>141039</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142163</t>
+          <t>136244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3663</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3714</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3735</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>38496</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>35916</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35608</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>39676</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>36679</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>90,08%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>137</t>
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>74189</t>
+          <t>74104</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71497</t>
+          <t>71473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48694</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>47323</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>44251</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>40860</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>45629</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>95,85%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>88,5%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>55828</t>
+          <t>43725</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54376</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45178</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>100079</t>
+          <t>92418</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96763</t>
+          <t>89203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101718</t>
+          <t>94072</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2660</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7977</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5082</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2203</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10168</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>14655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>138171</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>132854</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>139984</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>119426</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>114340</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>122305</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>152711</t>
+          <t>117433</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147898</t>
+          <t>112447</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154492</t>
+          <t>120338</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>272139</t>
+          <t>255604</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>266275</t>
+          <t>248706</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>275894</t>
+          <t>259198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140831</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140831</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140831</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155288</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>279797</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>279797</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>279797</t>
+          <t>263361</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>950</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3151,77 +3151,77 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5315</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5790</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4847</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3234,74 +3234,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>158471</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>153985</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>131175</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>129381</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>140112</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>138112</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>140497</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>98,3%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>155927</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>151480</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>156795</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -3309,27 +3309,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>287102</t>
+          <t>298584</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>283567</t>
+          <t>294128</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>688895</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>681246</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>693830</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>654761</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>648397</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>659367</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>749384</t>
+          <t>618295</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>741426</t>
+          <t>610887</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>754436</t>
+          <t>622599</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1404145</t>
+          <t>1307189</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1394883</t>
+          <t>1297430</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1411108</t>
+          <t>1314178</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
